--- a/wiki/reports/daily/2026-09-18_일일보고.xlsx
+++ b/wiki/reports/daily/2026-09-18_일일보고.xlsx
@@ -95,12 +95,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FADBD8"/>
+        <fgColor rgb="00D5F5E3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D5F5E3"/>
+        <fgColor rgb="00FADBD8"/>
       </patternFill>
     </fill>
     <fill>
@@ -155,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -195,6 +195,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -624,7 +630,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>생성: 2026-09-18 07:59   |   전일: 9월 17일   |   월평균 기준: 이전 작업일 13일 평균   |   9월 누적 작업일: 14일</t>
+          <t>생성: 2026-09-18 16:00   |   전일: 9월 17일   |   월평균 기준: 이전 작업일 13일 평균   |   9월 누적 작업일: 14일</t>
         </is>
       </c>
     </row>
@@ -686,25 +692,25 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>26</v>
       </c>
       <c r="D4" s="7" t="n">
-        <v>-6</v>
+        <v>4</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>-0.2307692307692308</v>
+        <v>0.1538461538461539</v>
       </c>
       <c r="F4" s="9" t="n">
         <v>28.9</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>-8.923076923076923</v>
+        <v>1.076923076923077</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>-0.3085106382978723</v>
+        <v>0.03723404255319148</v>
       </c>
       <c r="I4" s="10" t="inlineStr"/>
     </row>
@@ -715,29 +721,29 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>7840</v>
+        <v>10720</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>11202</v>
       </c>
-      <c r="D5" s="7" t="n">
-        <v>-3362</v>
-      </c>
-      <c r="E5" s="8" t="n">
-        <v>-0.3001249776825567</v>
+      <c r="D5" s="11" t="n">
+        <v>-482</v>
+      </c>
+      <c r="E5" s="12" t="n">
+        <v>-0.043028030708802</v>
       </c>
       <c r="F5" s="9" t="n">
         <v>7371.6</v>
       </c>
-      <c r="G5" s="11" t="n">
-        <v>468.3846153846152</v>
-      </c>
-      <c r="H5" s="12" t="n">
-        <v>0.06353893833936824</v>
+      <c r="G5" s="7" t="n">
+        <v>3348.384615384615</v>
+      </c>
+      <c r="H5" s="8" t="n">
+        <v>0.4542267116068913</v>
       </c>
       <c r="I5" s="10" t="inlineStr">
         <is>
-          <t>2:10:40</t>
+          <t>2:58:40</t>
         </is>
       </c>
     </row>
@@ -748,25 +754,25 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="D6" s="7" t="n">
-        <v>-38</v>
-      </c>
-      <c r="E6" s="8" t="n">
-        <v>-0.95</v>
+      <c r="D6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F6" s="9" t="n">
         <v>16.7</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>-14.69230769230769</v>
+        <v>23.30769230769231</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>-0.880184331797235</v>
+        <v>1.396313364055299</v>
       </c>
       <c r="I6" s="10" t="inlineStr"/>
     </row>
@@ -777,143 +783,143 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>2</v>
+        <v>17598</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>13790</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>-13788</v>
+        <v>3808</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>-0.9998549673676578</v>
+        <v>0.2761421319796954</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>6048.6</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>-6046.615384615385</v>
+        <v>11549.38461538462</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>-0.9996693458134093</v>
+        <v>1.909426187811578</v>
       </c>
       <c r="I7" s="10" t="inlineStr">
         <is>
-          <t>0:00:02</t>
+          <t>4:53:18</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>합계  수량 (개)</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>66</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>-44</v>
+        <v>4</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>-0.6666666666666666</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>45.6</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>-23.61538461538461</v>
+        <v>24.38461538461539</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>-0.5177065767284992</v>
+        <v>0.5345699831365937</v>
       </c>
       <c r="I8" s="10" t="inlineStr"/>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>합계  가공시간 (초)</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>7842</v>
+        <v>28318</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>24992</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>-17150</v>
+        <v>3326</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>-0.686219590268886</v>
+        <v>0.1330825864276569</v>
       </c>
       <c r="F9" s="9" t="n">
         <v>13420.2</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>-5578.23076923077</v>
+        <v>14897.76923076923</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>-0.4156583344319426</v>
+        <v>1.110097843095671</v>
       </c>
       <c r="I9" s="10" t="inlineStr">
         <is>
-          <t>2:10:42</t>
+          <t>7:51:58</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="14" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>합계  금액</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="C10" s="6" t="n">
         <v>66</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>-44</v>
+        <v>4</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>-0.6666666666666666</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>44.6</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>-22.61538461538461</v>
+        <v>25.38461538461539</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>-0.5068965517241379</v>
+        <v>0.5689655172413793</v>
       </c>
       <c r="I10" s="10" t="inlineStr"/>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>9월 누적  (14일 / 18일 중 작업일)</t>
         </is>
       </c>
-      <c r="B11" s="15" t="n"/>
-      <c r="C11" s="16" t="n">
-        <v>615</v>
-      </c>
-      <c r="D11" s="16" t="n">
-        <v>182305</v>
-      </c>
-      <c r="E11" s="16" t="n">
-        <v>602</v>
-      </c>
-      <c r="F11" s="15" t="n"/>
-      <c r="G11" s="15" t="n"/>
-      <c r="H11" s="15" t="n"/>
-      <c r="I11" s="15" t="n"/>
+      <c r="B11" s="17" t="n"/>
+      <c r="C11" s="18" t="n">
+        <v>663</v>
+      </c>
+      <c r="D11" s="18" t="n">
+        <v>202781</v>
+      </c>
+      <c r="E11" s="18" t="n">
+        <v>650</v>
+      </c>
+      <c r="F11" s="17" t="n"/>
+      <c r="G11" s="17" t="n"/>
+      <c r="H11" s="17" t="n"/>
+      <c r="I11" s="17" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -931,7 +937,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -955,272 +961,477 @@
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="17" t="inlineStr">
+      <c r="A2" s="19" t="inlineStr">
         <is>
           <t>■ FAST GRIND</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="18" t="inlineStr">
+      <c r="A3" s="20" t="inlineStr">
         <is>
           <t>순서</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="20" t="inlineStr">
         <is>
           <t>형상</t>
         </is>
       </c>
-      <c r="C3" s="18" t="inlineStr">
+      <c r="C3" s="20" t="inlineStr">
         <is>
           <t>날수(F)</t>
         </is>
       </c>
-      <c r="D3" s="18" t="inlineStr">
+      <c r="D3" s="20" t="inlineStr">
         <is>
           <t>날경(Ø)</t>
         </is>
       </c>
-      <c r="E3" s="18" t="inlineStr">
+      <c r="E3" s="20" t="inlineStr">
         <is>
           <t>상크경(Ø)</t>
         </is>
       </c>
-      <c r="F3" s="18" t="inlineStr">
+      <c r="F3" s="20" t="inlineStr">
         <is>
           <t>코팅</t>
         </is>
       </c>
-      <c r="G3" s="18" t="inlineStr">
+      <c r="G3" s="20" t="inlineStr">
         <is>
           <t>특이사항</t>
         </is>
       </c>
-      <c r="H3" s="18" t="inlineStr">
+      <c r="H3" s="20" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I3" s="18" t="inlineStr">
+      <c r="I3" s="20" t="inlineStr">
         <is>
           <t>수량(개)</t>
         </is>
       </c>
-      <c r="J3" s="18" t="inlineStr">
+      <c r="J3" s="20" t="inlineStr">
         <is>
           <t>시간합계(초)</t>
         </is>
       </c>
-      <c r="K3" s="18" t="inlineStr">
+      <c r="K3" s="20" t="inlineStr">
         <is>
           <t>시간(H:M:S)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="19" t="n">
+      <c r="A4" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="20" t="inlineStr">
+      <c r="B4" s="22" t="inlineStr">
         <is>
           <t>면취</t>
         </is>
       </c>
-      <c r="C4" s="19" t="n">
+      <c r="C4" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="D4" s="19" t="n">
+      <c r="D4" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="E4" s="19" t="n">
+      <c r="E4" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="F4" s="20" t="inlineStr">
+      <c r="F4" s="22" t="inlineStr">
         <is>
           <t>뮤</t>
         </is>
       </c>
-      <c r="G4" s="20" t="inlineStr">
+      <c r="G4" s="22" t="inlineStr">
         <is>
           <t>0303</t>
         </is>
       </c>
-      <c r="H4" s="19" t="inlineStr"/>
-      <c r="I4" s="21" t="n">
+      <c r="H4" s="21" t="inlineStr"/>
+      <c r="I4" s="23" t="n">
         <v>20</v>
       </c>
-      <c r="J4" s="21" t="n">
+      <c r="J4" s="23" t="n">
         <v>7840</v>
       </c>
-      <c r="K4" s="19" t="inlineStr">
+      <c r="K4" s="21" t="inlineStr">
         <is>
           <t>2:10:40</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>면취</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="E5" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="F5" s="22" t="inlineStr">
+        <is>
+          <t>비</t>
+        </is>
+      </c>
+      <c r="G5" s="22" t="inlineStr">
+        <is>
+          <t>0067</t>
+        </is>
+      </c>
+      <c r="H5" s="21" t="inlineStr"/>
+      <c r="I5" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="J5" s="23" t="n">
+        <v>864</v>
+      </c>
+      <c r="K5" s="21" t="inlineStr">
+        <is>
+          <t>0:14:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>면취</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="E6" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="F6" s="22" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G6" s="22" t="inlineStr">
+        <is>
+          <t>0104</t>
+        </is>
+      </c>
+      <c r="H6" s="21" t="inlineStr"/>
+      <c r="I6" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="J6" s="23" t="n">
+        <v>2016</v>
+      </c>
+      <c r="K6" s="21" t="inlineStr">
+        <is>
+          <t>0:33:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>FAST GRIND 소계</t>
         </is>
       </c>
-      <c r="B5" s="15" t="n"/>
-      <c r="C5" s="15" t="n"/>
-      <c r="D5" s="15" t="n"/>
-      <c r="E5" s="15" t="n"/>
-      <c r="F5" s="15" t="n"/>
-      <c r="G5" s="15" t="n"/>
-      <c r="H5" s="15" t="n"/>
-      <c r="I5" s="16" t="n">
-        <v>20</v>
-      </c>
-      <c r="J5" s="16" t="n">
-        <v>7840</v>
-      </c>
-      <c r="K5" s="15" t="inlineStr">
-        <is>
-          <t>2:10:40</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="22" t="inlineStr">
+      <c r="B7" s="17" t="n"/>
+      <c r="C7" s="17" t="n"/>
+      <c r="D7" s="17" t="n"/>
+      <c r="E7" s="17" t="n"/>
+      <c r="F7" s="17" t="n"/>
+      <c r="G7" s="17" t="n"/>
+      <c r="H7" s="17" t="n"/>
+      <c r="I7" s="18" t="n">
+        <v>30</v>
+      </c>
+      <c r="J7" s="18" t="n">
+        <v>10720</v>
+      </c>
+      <c r="K7" s="17" t="inlineStr">
+        <is>
+          <t>2:58:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="24" t="inlineStr">
         <is>
           <t>■ GX7</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="23" t="inlineStr">
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="25" t="inlineStr">
         <is>
           <t>순서</t>
         </is>
       </c>
-      <c r="B8" s="23" t="inlineStr">
+      <c r="B10" s="25" t="inlineStr">
         <is>
           <t>형상</t>
         </is>
       </c>
-      <c r="C8" s="23" t="inlineStr">
+      <c r="C10" s="25" t="inlineStr">
         <is>
           <t>날수(F)</t>
         </is>
       </c>
-      <c r="D8" s="23" t="inlineStr">
+      <c r="D10" s="25" t="inlineStr">
         <is>
           <t>날경(Ø)</t>
         </is>
       </c>
-      <c r="E8" s="23" t="inlineStr">
+      <c r="E10" s="25" t="inlineStr">
         <is>
           <t>상크경(Ø)</t>
         </is>
       </c>
-      <c r="F8" s="23" t="inlineStr">
+      <c r="F10" s="25" t="inlineStr">
         <is>
           <t>코팅</t>
         </is>
       </c>
-      <c r="G8" s="23" t="inlineStr">
+      <c r="G10" s="25" t="inlineStr">
         <is>
           <t>특이사항</t>
         </is>
       </c>
-      <c r="H8" s="23" t="inlineStr">
+      <c r="H10" s="25" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I8" s="23" t="inlineStr">
+      <c r="I10" s="25" t="inlineStr">
         <is>
           <t>수량(개)</t>
         </is>
       </c>
-      <c r="J8" s="23" t="inlineStr">
+      <c r="J10" s="25" t="inlineStr">
         <is>
           <t>시간합계(초)</t>
         </is>
       </c>
-      <c r="K8" s="23" t="inlineStr">
+      <c r="K10" s="25" t="inlineStr">
         <is>
           <t>시간(H:M:S)</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="24" t="n">
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="B11" s="27" t="inlineStr">
+        <is>
+          <t>평</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="n">
+        <v>6</v>
+      </c>
+      <c r="D11" s="26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" s="26" t="n">
+        <v>10</v>
+      </c>
+      <c r="F11" s="27" t="inlineStr">
+        <is>
+          <t>비</t>
+        </is>
+      </c>
+      <c r="G11" s="27" t="inlineStr">
+        <is>
+          <t>0301</t>
+        </is>
+      </c>
+      <c r="H11" s="26" t="inlineStr"/>
+      <c r="I11" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="28" t="n">
+        <v>360</v>
+      </c>
+      <c r="K11" s="26" t="inlineStr">
+        <is>
+          <t>0:06:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="B9" s="25" t="inlineStr">
+      <c r="B12" s="27" t="inlineStr">
         <is>
           <t>면취</t>
         </is>
       </c>
-      <c r="C9" s="24" t="n">
+      <c r="C12" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="D9" s="24" t="n">
+      <c r="D12" s="26" t="n">
         <v>10</v>
       </c>
-      <c r="E9" s="24" t="n">
+      <c r="E12" s="26" t="n">
         <v>10</v>
       </c>
-      <c r="F9" s="25" t="inlineStr">
+      <c r="F12" s="27" t="inlineStr">
         <is>
           <t>비</t>
         </is>
       </c>
-      <c r="G9" s="25" t="inlineStr">
+      <c r="G12" s="27" t="inlineStr">
         <is>
           <t>0126_샘플 요청 건</t>
         </is>
       </c>
-      <c r="H9" s="24" t="inlineStr"/>
-      <c r="I9" s="26" t="n">
+      <c r="H12" s="26" t="inlineStr"/>
+      <c r="I12" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="J9" s="26" t="n">
+      <c r="J12" s="28" t="n">
+        <v>884</v>
+      </c>
+      <c r="K12" s="26" t="inlineStr">
+        <is>
+          <t>0:14:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" s="27" t="inlineStr">
+        <is>
+          <t>면취</t>
+        </is>
+      </c>
+      <c r="C13" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="K9" s="24" t="inlineStr">
-        <is>
-          <t>0:00:02</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="D13" s="26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" s="26" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" s="27" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G13" s="27" t="inlineStr">
+        <is>
+          <t>0104 ㅋㅌ</t>
+        </is>
+      </c>
+      <c r="H13" s="26" t="inlineStr"/>
+      <c r="I13" s="28" t="n">
+        <v>6</v>
+      </c>
+      <c r="J13" s="28" t="n">
+        <v>2652</v>
+      </c>
+      <c r="K13" s="26" t="inlineStr">
+        <is>
+          <t>0:44:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="B14" s="27" t="inlineStr">
+        <is>
+          <t>면취</t>
+        </is>
+      </c>
+      <c r="C14" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" s="26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" s="26" t="n">
+        <v>10</v>
+      </c>
+      <c r="F14" s="27" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G14" s="27" t="inlineStr">
+        <is>
+          <t>0303</t>
+        </is>
+      </c>
+      <c r="H14" s="26" t="inlineStr"/>
+      <c r="I14" s="28" t="n">
+        <v>31</v>
+      </c>
+      <c r="J14" s="28" t="n">
+        <v>13702</v>
+      </c>
+      <c r="K14" s="26" t="inlineStr">
+        <is>
+          <t>3:48:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>GX7 소계</t>
         </is>
       </c>
-      <c r="B10" s="15" t="n"/>
-      <c r="C10" s="15" t="n"/>
-      <c r="D10" s="15" t="n"/>
-      <c r="E10" s="15" t="n"/>
-      <c r="F10" s="15" t="n"/>
-      <c r="G10" s="15" t="n"/>
-      <c r="H10" s="15" t="n"/>
-      <c r="I10" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="J10" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="K10" s="15" t="inlineStr">
-        <is>
-          <t>0:00:02</t>
+      <c r="B15" s="17" t="n"/>
+      <c r="C15" s="17" t="n"/>
+      <c r="D15" s="17" t="n"/>
+      <c r="E15" s="17" t="n"/>
+      <c r="F15" s="17" t="n"/>
+      <c r="G15" s="17" t="n"/>
+      <c r="H15" s="17" t="n"/>
+      <c r="I15" s="18" t="n">
+        <v>40</v>
+      </c>
+      <c r="J15" s="18" t="n">
+        <v>17598</v>
+      </c>
+      <c r="K15" s="17" t="inlineStr">
+        <is>
+          <t>4:53:18</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A7:K7"/>
-    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A7:H7"/>
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A5:H5"/>
     <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A9:K9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
